--- a/output/pdf_financials_xlsx/TCEC.xlsx
+++ b/output/pdf_financials_xlsx/TCEC.xlsx
@@ -1928,13 +1928,13 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>0.7467780000000001</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>1.050383</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>1.772659</v>
       </c>
     </row>
     <row r="93">
@@ -2335,13 +2335,13 @@
         </is>
       </c>
       <c r="B118" s="3" t="n">
-        <v>0</v>
+        <v>-0.495901</v>
       </c>
       <c r="C118" s="3" t="n">
-        <v>0</v>
+        <v>-0.321009</v>
       </c>
       <c r="D118" s="3" t="n">
-        <v>0</v>
+        <v>-2.030152</v>
       </c>
     </row>
     <row r="119">
@@ -3030,7 +3030,11 @@
           <t>Reserves (Note 9)</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E13" t="inlineStr">
         <is>
           <t>-</t>
@@ -3192,7 +3196,11 @@
           <t>Reserves (Note 10)</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr"/>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E19" s="5" t="n">
         <v>0.7467780000000001</v>
       </c>
@@ -3502,7 +3510,11 @@
           <t>Exploration and evaluation assets expenditures</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr"/>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E29" s="5" t="n">
         <v>-0.495901</v>
       </c>

--- a/output/pdf_financials_xlsx/TCEC.xlsx
+++ b/output/pdf_financials_xlsx/TCEC.xlsx
@@ -609,13 +609,13 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.032234</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>3e-05</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.012434</v>
       </c>
     </row>
     <row r="13">
@@ -861,13 +861,13 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-1.07806</v>
+        <v>-1.110294</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-2.851048</v>
+        <v>-2.851078</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-1.561911</v>
+        <v>-1.574345</v>
       </c>
     </row>
     <row r="28">
@@ -893,13 +893,13 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-1.07806</v>
+        <v>-1.110294</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-2.851048</v>
+        <v>-2.851078</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-1.561911</v>
+        <v>-1.574345</v>
       </c>
     </row>
     <row r="30">
@@ -976,13 +976,13 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.693566</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>3.086625</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>1.937146</v>
       </c>
     </row>
     <row r="35">
@@ -1008,13 +1008,13 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.693566</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>3.086625</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>1.937146</v>
       </c>
     </row>
     <row r="37">
@@ -1200,13 +1200,13 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>1.249818</v>
+        <v>0.556252</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>3.21999</v>
+        <v>0.133365</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>2.073217</v>
+        <v>0.136071</v>
       </c>
     </row>
     <row r="49">
@@ -2697,7 +2697,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">
@@ -4452,7 +4452,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E59" s="5" t="n">
